--- a/output/pdf_financials_xlsx/VC.X.xlsx
+++ b/output/pdf_financials_xlsx/VC.X.xlsx
@@ -2227,16 +2227,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.180529</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.180529</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.180529</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.180529</v>
       </c>
     </row>
     <row r="93">
@@ -3440,7 +3440,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3986,7 +3990,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -4206,7 +4214,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>0.180529</v>
       </c>

--- a/output/pdf_financials_xlsx/VC.X.xlsx
+++ b/output/pdf_financials_xlsx/VC.X.xlsx
@@ -642,10 +642,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003458</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000382</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -947,10 +947,10 @@
         <v>-1.057712</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-10.852429</v>
+        <v>-10.855887</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.022706</v>
+        <v>-0.023088</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.318331</v>
@@ -985,10 +985,10 @@
         <v>-1.057712</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-10.852429</v>
+        <v>-10.855887</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.022706</v>
+        <v>-0.023088</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.318331</v>
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.002578</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001511</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.005422</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.00197</v>
       </c>
     </row>
     <row r="35">
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.071975</v>
+        <v>0.07455299999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.021545</v>
+        <v>0.023056</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.13325</v>
+        <v>0.138672</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.000772</v>
+        <v>0.002742</v>
       </c>
     </row>
     <row r="37">
@@ -1347,16 +1347,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.002578</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.001511</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.005422</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.00197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
@@ -3770,7 +3770,11 @@
           <t>Reclamation deposit (Note 3)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -4104,7 +4108,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>0.03</v>
       </c>
@@ -6562,7 +6570,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7252,7 +7260,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7326,7 +7334,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">

--- a/output/pdf_financials_xlsx/VC.X.xlsx
+++ b/output/pdf_financials_xlsx/VC.X.xlsx
@@ -1681,10 +1681,10 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.177997</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>1.330718</v>
       </c>
     </row>
     <row r="65">
@@ -1760,7 +1760,7 @@
         <v>1.205997</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>1.356718</v>
+        <v>2.687436</v>
       </c>
     </row>
     <row r="69">
@@ -2641,16 +2641,16 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.157196</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-0.014923</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-0.07516</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-0.021183</v>
       </c>
     </row>
     <row r="115">
@@ -4668,7 +4668,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -5468,7 +5472,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>-0.157196</v>
       </c>
@@ -6188,7 +6196,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
         <v>1.4425</v>
       </c>
